--- a/data/trans_orig/IP07C06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>21107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>27787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>25974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61104</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75251</t>
+          <t>74988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2151</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13889</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>27104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>37250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46448</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>24133</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>39182</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27065</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22211</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32982</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>31386</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>44210</t>
+          <t>44369</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>67487</t>
+          <t>68881</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>82909</t>
+          <t>83393</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>18176</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>46171</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>52165</t>
+          <t>52769</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>76965</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>95440</t>
+          <t>95114</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>126408</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>170047</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196278</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>221918</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>371172</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>408075</t>
+          <t>408622</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>45140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7808,77 +7808,77 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4342</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8796</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>10,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4342</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9334</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>10544</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37463</t>
+          <t>37077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44278</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>63554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78219</t>
+          <t>78530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20468</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37370</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41193</t>
+          <t>41023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,22%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>31416</t>
+          <t>31378</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40648</t>
+          <t>41318</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>77,45%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27398</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>35802</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>35020</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>48842</t>
+          <t>48685</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>66013</t>
+          <t>65696</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18305</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>33603</t>
+          <t>31904</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>28415</t>
+          <t>28426</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>41680</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>57181</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>77287</t>
+          <t>76506</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>85494</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>116026</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>73308</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>159391</t>
+          <t>158722</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>188221</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>174505</t>
+          <t>173440</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>203625</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>342251</t>
+          <t>342725</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>384527</t>
+          <t>383667</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7721</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39540</t>
+          <t>39780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>43742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>52547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87094</t>
+          <t>86514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98860</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>839</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>28197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28555</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61704</t>
+          <t>61847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,49 +15767,49 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>27,44%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>9823</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>26,61%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>9781</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15776</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11155</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>41065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -16213,7 +16213,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16547,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16675,12 +16675,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16910,7 +16910,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,51%</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>31191</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>44543</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>71870</t>
+          <t>72096</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>90607</t>
+          <t>91186</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29663</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>21351</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41710</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>37189</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>54908</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>18378</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>58025</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>54815</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>80223</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>176228</t>
+          <t>174457</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>214667</t>
+          <t>216364</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>176833</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>210486</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>374696</t>
+          <t>370732</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>415294</t>
+          <t>415043</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
